--- a/MoEYS_Students_Export.xlsx
+++ b/MoEYS_Students_Export.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N164"/>
+  <dimension ref="A1:P164"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -415,9 +415,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,12 +457,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -499,12 +507,18 @@
         <v>ចាន់ សុខា</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>កែវ ស្រីពៅ</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 341 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -543,12 +557,18 @@
         <v>សុខ ចាន់ថន</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>089 667 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -587,12 +607,18 @@
         <v>ហេង សម្បត្តិ</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ឡុង ធីតា</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>017 889 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -631,12 +657,18 @@
         <v>គង់ សុវណ្ណ</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>សេង មុនីកា</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>098 554 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -675,12 +707,18 @@
         <v>ម៉ៅ វិចិត្រ</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ទាវ សុផល</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>070 223 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -719,12 +757,18 @@
         <v>ឈុន សំអាត</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ង៉ែត សុភ័ក្រ</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>011 445 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -763,12 +807,18 @@
         <v>តាំង ហុកសេង</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>លឹម គឹមហួរ</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 998 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -807,12 +857,18 @@
         <v>ស៊ុន វណ្ណារ៉ា</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>យឹម ស្រីនាង</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>097 334 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -851,12 +907,18 @@
         <v>លាង សុវណ្ណ</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>សោម ចរិយា</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>015 776 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -895,12 +957,18 @@
         <v>អ៊ុំ សារ៉េត</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ពៅ សុភី</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>085 221 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -939,12 +1007,18 @@
         <v>ឌួង រិទ្ធី</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>លាង សុខេង</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>077 889 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -983,12 +1057,18 @@
         <v>នូ សារុន</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ហុង ពិសី</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>096 443 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1027,12 +1107,18 @@
         <v>ឡាយ សុវណ្ណា</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ជុំ ចរិយា</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 667 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1071,12 +1157,18 @@
         <v>វ៉ាន់ គង់</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>សោម ធីតា</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>098 112 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1115,12 +1207,18 @@
         <v>ជា សុវណ្ណ</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម៉ៅ គឹមលាង</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>089 334 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1159,12 +1257,18 @@
         <v>កែវ សុជាតិ</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ស៊ុន ផល្លា</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>017 556 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1203,12 +1307,18 @@
         <v>រស់ គឹមស៊ន</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ខៀវ គឹមអាន</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>010 778 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1247,12 +1357,18 @@
         <v>សេង វណ្ណឌី</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 889 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1291,12 +1407,18 @@
         <v>ណុប ផល</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ចាន់ ស្រីអូន</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>077 990 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1335,12 +1457,18 @@
         <v>យឹម វិចិត្រ</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម៉ី សុខុម</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>061 223 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1379,12 +1507,18 @@
         <v>អ៊ុក គឹមហេង</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ចាន់ ស្រីមុំ</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 445 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1423,12 +1557,18 @@
         <v>ហុង សារ៉ុម</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>នូ សារុន</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>015 667 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1467,12 +1607,18 @@
         <v>លី សុខុម</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ទេព ធីតា</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>097 889 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1511,12 +1657,18 @@
         <v>ទេព សុវណ្ណ</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>070 112 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1555,12 +1707,18 @@
         <v>ពេជ្រ សារ៉េត</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>សេង ផល្លា</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>089 443 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1599,12 +1757,18 @@
         <v>សោម ប៊ុនធឿន</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម៉ៅ វណ្ណី</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>016 554 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1643,12 +1807,18 @@
         <v>ខៀវ គឹមអាន</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>រស់ សុភី</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 334 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1687,12 +1857,18 @@
         <v>ភួង សំអុល</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ចាន់ ស្រីមុំ</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>098 776 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1731,12 +1907,18 @@
         <v>អៀង វណ្ណា</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ឡាយ ស្រីពៅ</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>085 990 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1775,12 +1957,18 @@
         <v>ឡុង វិចិត្រ</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ស៊ុន ធីតា</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>017 221 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1819,12 +2007,18 @@
         <v>ឪពុក សុខ រិទ្ធី</v>
       </c>
       <c r="L32" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M32" t="str">
         <v>ម្តាយ សុខ រិទ្ធី</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O32" t="str">
         <v>012 150 001</v>
       </c>
-      <c r="N32" t="str">
+      <c r="P32" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1863,12 +2057,18 @@
         <v>ឪពុក សុខ ស្រីពេជ្រ</v>
       </c>
       <c r="L33" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M33" t="str">
         <v>ម្តាយ សុខ ស្រីពេជ្រ</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O33" t="str">
         <v>012 150 002</v>
       </c>
-      <c r="N33" t="str">
+      <c r="P33" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1907,12 +2107,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L34" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M34" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O34" t="str">
         <v>012 150 003</v>
       </c>
-      <c r="N34" t="str">
+      <c r="P34" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1951,12 +2157,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L35" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M35" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O35" t="str">
         <v>012 150 004</v>
       </c>
-      <c r="N35" t="str">
+      <c r="P35" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -1995,12 +2207,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L36" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M36" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O36" t="str">
         <v>012 150 005</v>
       </c>
-      <c r="N36" t="str">
+      <c r="P36" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2039,12 +2257,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L37" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M37" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O37" t="str">
         <v>012 150 006</v>
       </c>
-      <c r="N37" t="str">
+      <c r="P37" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2083,12 +2307,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L38" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M38" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O38" t="str">
         <v>012 150 007</v>
       </c>
-      <c r="N38" t="str">
+      <c r="P38" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2127,12 +2357,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L39" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M39" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O39" t="str">
         <v>012 150 008</v>
       </c>
-      <c r="N39" t="str">
+      <c r="P39" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2171,12 +2407,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L40" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M40" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O40" t="str">
         <v>012 150 009</v>
       </c>
-      <c r="N40" t="str">
+      <c r="P40" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2215,12 +2457,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L41" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M41" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O41" t="str">
         <v>012 150 010</v>
       </c>
-      <c r="N41" t="str">
+      <c r="P41" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2259,12 +2507,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L42" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M42" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O42" t="str">
         <v>012 150 011</v>
       </c>
-      <c r="N42" t="str">
+      <c r="P42" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2303,12 +2557,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L43" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M43" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O43" t="str">
         <v>012 150 012</v>
       </c>
-      <c r="N43" t="str">
+      <c r="P43" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2347,12 +2607,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L44" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M44" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O44" t="str">
         <v>012 150 013</v>
       </c>
-      <c r="N44" t="str">
+      <c r="P44" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2391,12 +2657,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L45" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M45" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O45" t="str">
         <v>012 150 014</v>
       </c>
-      <c r="N45" t="str">
+      <c r="P45" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2435,12 +2707,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L46" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M46" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O46" t="str">
         <v>012 150 015</v>
       </c>
-      <c r="N46" t="str">
+      <c r="P46" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2479,12 +2757,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L47" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M47" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O47" t="str">
         <v>012 150 016</v>
       </c>
-      <c r="N47" t="str">
+      <c r="P47" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2523,12 +2807,18 @@
         <v>ឪពុក សុខ រិទ្ធី</v>
       </c>
       <c r="L48" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M48" t="str">
         <v>ម្តាយ សុខ រិទ្ធី</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O48" t="str">
         <v>012 150 017</v>
       </c>
-      <c r="N48" t="str">
+      <c r="P48" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2567,12 +2857,18 @@
         <v>ឪពុក សុខ ស្រីពេជ្រ</v>
       </c>
       <c r="L49" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M49" t="str">
         <v>ម្តាយ សុខ ស្រីពេជ្រ</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O49" t="str">
         <v>012 150 018</v>
       </c>
-      <c r="N49" t="str">
+      <c r="P49" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2611,12 +2907,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L50" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M50" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O50" t="str">
         <v>012 150 019</v>
       </c>
-      <c r="N50" t="str">
+      <c r="P50" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2655,12 +2957,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L51" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M51" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O51" t="str">
         <v>012 150 020</v>
       </c>
-      <c r="N51" t="str">
+      <c r="P51" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2699,12 +3007,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L52" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M52" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O52" t="str">
         <v>012 150 021</v>
       </c>
-      <c r="N52" t="str">
+      <c r="P52" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2743,12 +3057,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L53" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M53" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O53" t="str">
         <v>012 150 022</v>
       </c>
-      <c r="N53" t="str">
+      <c r="P53" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2787,12 +3107,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L54" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M54" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O54" t="str">
         <v>012 150 023</v>
       </c>
-      <c r="N54" t="str">
+      <c r="P54" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2831,12 +3157,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L55" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M55" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O55" t="str">
         <v>012 150 024</v>
       </c>
-      <c r="N55" t="str">
+      <c r="P55" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2875,12 +3207,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L56" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M56" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O56" t="str">
         <v>012 150 025</v>
       </c>
-      <c r="N56" t="str">
+      <c r="P56" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2919,12 +3257,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L57" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M57" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O57" t="str">
         <v>012 150 026</v>
       </c>
-      <c r="N57" t="str">
+      <c r="P57" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -2963,12 +3307,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L58" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M58" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O58" t="str">
         <v>012 150 027</v>
       </c>
-      <c r="N58" t="str">
+      <c r="P58" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3007,12 +3357,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L59" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M59" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O59" t="str">
         <v>012 150 028</v>
       </c>
-      <c r="N59" t="str">
+      <c r="P59" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3051,12 +3407,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L60" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M60" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O60" t="str">
         <v>012 150 029</v>
       </c>
-      <c r="N60" t="str">
+      <c r="P60" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3095,12 +3457,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L61" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M61" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O61" t="str">
         <v>012 150 030</v>
       </c>
-      <c r="N61" t="str">
+      <c r="P61" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3139,12 +3507,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L62" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M62" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O62" t="str">
         <v>012 150 031</v>
       </c>
-      <c r="N62" t="str">
+      <c r="P62" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3183,12 +3557,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L63" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M63" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O63" t="str">
         <v>012 150 032</v>
       </c>
-      <c r="N63" t="str">
+      <c r="P63" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3227,12 +3607,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L64" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M64" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O64" t="str">
         <v>012 130 001</v>
       </c>
-      <c r="N64" t="str">
+      <c r="P64" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3271,12 +3657,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L65" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M65" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O65" t="str">
         <v>012 130 002</v>
       </c>
-      <c r="N65" t="str">
+      <c r="P65" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3315,12 +3707,18 @@
         <v>ឪពុក ចាន់ សុភ័ក្ត្រ</v>
       </c>
       <c r="L66" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M66" t="str">
         <v>ម្តាយ ចាន់ សុភ័ក្ត្រ</v>
       </c>
-      <c r="M66" t="str">
+      <c r="N66" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O66" t="str">
         <v>012 130 003</v>
       </c>
-      <c r="N66" t="str">
+      <c r="P66" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3359,12 +3757,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L67" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M67" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M67" t="str">
+      <c r="N67" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O67" t="str">
         <v>012 130 004</v>
       </c>
-      <c r="N67" t="str">
+      <c r="P67" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3403,12 +3807,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L68" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M68" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M68" t="str">
+      <c r="N68" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O68" t="str">
         <v>012 130 005</v>
       </c>
-      <c r="N68" t="str">
+      <c r="P68" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3447,12 +3857,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L69" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M69" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O69" t="str">
         <v>012 130 006</v>
       </c>
-      <c r="N69" t="str">
+      <c r="P69" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3491,12 +3907,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L70" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M70" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O70" t="str">
         <v>012 130 007</v>
       </c>
-      <c r="N70" t="str">
+      <c r="P70" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3535,12 +3957,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L71" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M71" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O71" t="str">
         <v>012 130 008</v>
       </c>
-      <c r="N71" t="str">
+      <c r="P71" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3579,12 +4007,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L72" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M72" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O72" t="str">
         <v>012 130 009</v>
       </c>
-      <c r="N72" t="str">
+      <c r="P72" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3623,12 +4057,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L73" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M73" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O73" t="str">
         <v>012 130 010</v>
       </c>
-      <c r="N73" t="str">
+      <c r="P73" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3667,12 +4107,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L74" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M74" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O74" t="str">
         <v>012 130 011</v>
       </c>
-      <c r="N74" t="str">
+      <c r="P74" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3711,12 +4157,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L75" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M75" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O75" t="str">
         <v>012 130 012</v>
       </c>
-      <c r="N75" t="str">
+      <c r="P75" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3755,12 +4207,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L76" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M76" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M76" t="str">
+      <c r="N76" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O76" t="str">
         <v>012 130 013</v>
       </c>
-      <c r="N76" t="str">
+      <c r="P76" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3799,12 +4257,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L77" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M77" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M77" t="str">
+      <c r="N77" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O77" t="str">
         <v>012 130 014</v>
       </c>
-      <c r="N77" t="str">
+      <c r="P77" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3843,12 +4307,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L78" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M78" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M78" t="str">
+      <c r="N78" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O78" t="str">
         <v>012 130 015</v>
       </c>
-      <c r="N78" t="str">
+      <c r="P78" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3887,12 +4357,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L79" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M79" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O79" t="str">
         <v>012 130 016</v>
       </c>
-      <c r="N79" t="str">
+      <c r="P79" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3931,12 +4407,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L80" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M80" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M80" t="str">
+      <c r="N80" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O80" t="str">
         <v>012 130 017</v>
       </c>
-      <c r="N80" t="str">
+      <c r="P80" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -3975,12 +4457,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L81" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M81" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M81" t="str">
+      <c r="N81" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O81" t="str">
         <v>012 130 018</v>
       </c>
-      <c r="N81" t="str">
+      <c r="P81" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4019,12 +4507,18 @@
         <v>ឪពុក ចាន់ សុភ័ក្ត្រ</v>
       </c>
       <c r="L82" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M82" t="str">
         <v>ម្តាយ ចាន់ សុភ័ក្ត្រ</v>
       </c>
-      <c r="M82" t="str">
+      <c r="N82" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O82" t="str">
         <v>012 130 019</v>
       </c>
-      <c r="N82" t="str">
+      <c r="P82" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4063,12 +4557,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L83" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M83" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M83" t="str">
+      <c r="N83" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O83" t="str">
         <v>012 130 020</v>
       </c>
-      <c r="N83" t="str">
+      <c r="P83" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4107,12 +4607,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L84" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M84" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M84" t="str">
+      <c r="N84" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O84" t="str">
         <v>012 130 021</v>
       </c>
-      <c r="N84" t="str">
+      <c r="P84" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4151,12 +4657,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L85" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M85" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M85" t="str">
+      <c r="N85" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O85" t="str">
         <v>012 130 022</v>
       </c>
-      <c r="N85" t="str">
+      <c r="P85" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4195,12 +4707,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L86" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M86" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O86" t="str">
         <v>012 130 023</v>
       </c>
-      <c r="N86" t="str">
+      <c r="P86" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4239,12 +4757,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L87" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M87" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M87" t="str">
+      <c r="N87" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O87" t="str">
         <v>012 130 024</v>
       </c>
-      <c r="N87" t="str">
+      <c r="P87" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4283,12 +4807,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L88" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M88" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M88" t="str">
+      <c r="N88" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O88" t="str">
         <v>012 130 025</v>
       </c>
-      <c r="N88" t="str">
+      <c r="P88" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4327,12 +4857,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L89" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M89" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M89" t="str">
+      <c r="N89" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O89" t="str">
         <v>012 130 026</v>
       </c>
-      <c r="N89" t="str">
+      <c r="P89" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4371,12 +4907,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L90" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M90" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M90" t="str">
+      <c r="N90" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O90" t="str">
         <v>012 130 027</v>
       </c>
-      <c r="N90" t="str">
+      <c r="P90" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4415,12 +4957,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L91" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M91" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M91" t="str">
+      <c r="N91" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O91" t="str">
         <v>012 130 028</v>
       </c>
-      <c r="N91" t="str">
+      <c r="P91" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4459,12 +5007,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L92" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M92" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M92" t="str">
+      <c r="N92" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O92" t="str">
         <v>012 130 029</v>
       </c>
-      <c r="N92" t="str">
+      <c r="P92" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4503,12 +5057,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L93" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M93" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O93" t="str">
         <v>012 130 030</v>
       </c>
-      <c r="N93" t="str">
+      <c r="P93" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4547,12 +5107,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L94" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M94" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M94" t="str">
+      <c r="N94" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O94" t="str">
         <v>012 130 031</v>
       </c>
-      <c r="N94" t="str">
+      <c r="P94" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4591,12 +5157,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L95" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M95" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M95" t="str">
+      <c r="N95" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O95" t="str">
         <v>012 130 032</v>
       </c>
-      <c r="N95" t="str">
+      <c r="P95" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4635,12 +5207,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L96" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M96" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M96" t="str">
+      <c r="N96" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O96" t="str">
         <v>012 130 033</v>
       </c>
-      <c r="N96" t="str">
+      <c r="P96" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4679,12 +5257,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L97" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M97" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M97" t="str">
+      <c r="N97" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O97" t="str">
         <v>012 130 034</v>
       </c>
-      <c r="N97" t="str">
+      <c r="P97" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4723,12 +5307,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L98" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M98" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M98" t="str">
+      <c r="N98" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O98" t="str">
         <v>012 090 001</v>
       </c>
-      <c r="N98" t="str">
+      <c r="P98" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4767,12 +5357,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L99" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M99" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M99" t="str">
+      <c r="N99" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O99" t="str">
         <v>012 090 002</v>
       </c>
-      <c r="N99" t="str">
+      <c r="P99" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4811,12 +5407,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L100" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M100" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O100" t="str">
         <v>012 090 003</v>
       </c>
-      <c r="N100" t="str">
+      <c r="P100" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4855,12 +5457,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L101" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M101" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M101" t="str">
+      <c r="N101" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O101" t="str">
         <v>012 090 004</v>
       </c>
-      <c r="N101" t="str">
+      <c r="P101" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4899,12 +5507,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L102" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M102" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M102" t="str">
+      <c r="N102" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O102" t="str">
         <v>012 090 005</v>
       </c>
-      <c r="N102" t="str">
+      <c r="P102" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4943,12 +5557,18 @@
         <v>ឪពុក លឹម គឹមហួរ</v>
       </c>
       <c r="L103" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M103" t="str">
         <v>ម្តាយ លឹម គឹមហួរ</v>
       </c>
-      <c r="M103" t="str">
+      <c r="N103" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O103" t="str">
         <v>012 090 006</v>
       </c>
-      <c r="N103" t="str">
+      <c r="P103" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -4987,12 +5607,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L104" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M104" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M104" t="str">
+      <c r="N104" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O104" t="str">
         <v>012 090 007</v>
       </c>
-      <c r="N104" t="str">
+      <c r="P104" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5031,12 +5657,18 @@
         <v>ឪពុក អ៊ុក ស្រីពេជ្រ</v>
       </c>
       <c r="L105" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M105" t="str">
         <v>ម្តាយ អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M105" t="str">
+      <c r="N105" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O105" t="str">
         <v>012 090 008</v>
       </c>
-      <c r="N105" t="str">
+      <c r="P105" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5075,12 +5707,18 @@
         <v>ឪពុក សេង វណ្ណឌី</v>
       </c>
       <c r="L106" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M106" t="str">
         <v>ម្តាយ សេង វណ្ណឌី</v>
       </c>
-      <c r="M106" t="str">
+      <c r="N106" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O106" t="str">
         <v>012 090 009</v>
       </c>
-      <c r="N106" t="str">
+      <c r="P106" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5119,12 +5757,18 @@
         <v>ឪពុក ឈុន សុភ័ក្ត្រ</v>
       </c>
       <c r="L107" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M107" t="str">
         <v>ម្តាយ ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O107" t="str">
         <v>012 090 010</v>
       </c>
-      <c r="N107" t="str">
+      <c r="P107" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5163,12 +5807,18 @@
         <v>ឪពុក ឈុន ពិសិដ្ឋ</v>
       </c>
       <c r="L108" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M108" t="str">
         <v>ម្តាយ ឈុន ពិសិដ្ឋ</v>
       </c>
-      <c r="M108" t="str">
+      <c r="N108" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O108" t="str">
         <v>012 090 011</v>
       </c>
-      <c r="N108" t="str">
+      <c r="P108" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5207,12 +5857,18 @@
         <v>ឪពុក ស៊ុន ស្រីកែវ</v>
       </c>
       <c r="L109" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M109" t="str">
         <v>ម្តាយ ស៊ុន ស្រីកែវ</v>
       </c>
-      <c r="M109" t="str">
+      <c r="N109" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O109" t="str">
         <v>012 090 012</v>
       </c>
-      <c r="N109" t="str">
+      <c r="P109" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5251,12 +5907,18 @@
         <v>ឪពុក ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
       <c r="L110" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M110" t="str">
         <v>ម្តាយ ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M110" t="str">
+      <c r="N110" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O110" t="str">
         <v>012 090 013</v>
       </c>
-      <c r="N110" t="str">
+      <c r="P110" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5295,12 +5957,18 @@
         <v>ឪពុក ហុង ពិសី</v>
       </c>
       <c r="L111" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M111" t="str">
         <v>ម្តាយ ហុង ពិសី</v>
       </c>
-      <c r="M111" t="str">
+      <c r="N111" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O111" t="str">
         <v>012 090 014</v>
       </c>
-      <c r="N111" t="str">
+      <c r="P111" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5339,12 +6007,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L112" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M112" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M112" t="str">
+      <c r="N112" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O112" t="str">
         <v>012 090 015</v>
       </c>
-      <c r="N112" t="str">
+      <c r="P112" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5383,12 +6057,18 @@
         <v>ឪពុក សោម ចរិយា</v>
       </c>
       <c r="L113" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M113" t="str">
         <v>ម្តាយ សោម ចរិយា</v>
       </c>
-      <c r="M113" t="str">
+      <c r="N113" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O113" t="str">
         <v>012 090 016</v>
       </c>
-      <c r="N113" t="str">
+      <c r="P113" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5427,12 +6107,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L114" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M114" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O114" t="str">
         <v>012 090 017</v>
       </c>
-      <c r="N114" t="str">
+      <c r="P114" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5471,12 +6157,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L115" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M115" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M115" t="str">
+      <c r="N115" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O115" t="str">
         <v>012 090 018</v>
       </c>
-      <c r="N115" t="str">
+      <c r="P115" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5515,12 +6207,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L116" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M116" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M116" t="str">
+      <c r="N116" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O116" t="str">
         <v>012 090 019</v>
       </c>
-      <c r="N116" t="str">
+      <c r="P116" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5559,12 +6257,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L117" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M117" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M117" t="str">
+      <c r="N117" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O117" t="str">
         <v>012 090 020</v>
       </c>
-      <c r="N117" t="str">
+      <c r="P117" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5603,12 +6307,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L118" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M118" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M118" t="str">
+      <c r="N118" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O118" t="str">
         <v>012 090 021</v>
       </c>
-      <c r="N118" t="str">
+      <c r="P118" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5647,12 +6357,18 @@
         <v>ឪពុក លឹម គឹមហួរ</v>
       </c>
       <c r="L119" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M119" t="str">
         <v>ម្តាយ លឹម គឹមហួរ</v>
       </c>
-      <c r="M119" t="str">
+      <c r="N119" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O119" t="str">
         <v>012 090 022</v>
       </c>
-      <c r="N119" t="str">
+      <c r="P119" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5691,12 +6407,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L120" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M120" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M120" t="str">
+      <c r="N120" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O120" t="str">
         <v>012 090 023</v>
       </c>
-      <c r="N120" t="str">
+      <c r="P120" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5735,12 +6457,18 @@
         <v>ឪពុក អ៊ុក ស្រីពេជ្រ</v>
       </c>
       <c r="L121" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M121" t="str">
         <v>ម្តាយ អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O121" t="str">
         <v>012 090 024</v>
       </c>
-      <c r="N121" t="str">
+      <c r="P121" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5779,12 +6507,18 @@
         <v>ឪពុក សេង វណ្ណឌី</v>
       </c>
       <c r="L122" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M122" t="str">
         <v>ម្តាយ សេង វណ្ណឌី</v>
       </c>
-      <c r="M122" t="str">
+      <c r="N122" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O122" t="str">
         <v>012 090 025</v>
       </c>
-      <c r="N122" t="str">
+      <c r="P122" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5823,12 +6557,18 @@
         <v>ឪពុក ឈុន សុភ័ក្ត្រ</v>
       </c>
       <c r="L123" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M123" t="str">
         <v>ម្តាយ ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M123" t="str">
+      <c r="N123" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O123" t="str">
         <v>012 090 026</v>
       </c>
-      <c r="N123" t="str">
+      <c r="P123" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5867,12 +6607,18 @@
         <v>ឪពុក ឈុន ពិសិដ្ឋ</v>
       </c>
       <c r="L124" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M124" t="str">
         <v>ម្តាយ ឈុន ពិសិដ្ឋ</v>
       </c>
-      <c r="M124" t="str">
+      <c r="N124" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O124" t="str">
         <v>012 090 027</v>
       </c>
-      <c r="N124" t="str">
+      <c r="P124" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5911,12 +6657,18 @@
         <v>ឪពុក ស៊ុន ស្រីកែវ</v>
       </c>
       <c r="L125" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M125" t="str">
         <v>ម្តាយ ស៊ុន ស្រីកែវ</v>
       </c>
-      <c r="M125" t="str">
+      <c r="N125" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O125" t="str">
         <v>012 090 028</v>
       </c>
-      <c r="N125" t="str">
+      <c r="P125" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5955,12 +6707,18 @@
         <v>ឪពុក ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
       <c r="L126" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M126" t="str">
         <v>ម្តាយ ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M126" t="str">
+      <c r="N126" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O126" t="str">
         <v>012 090 029</v>
       </c>
-      <c r="N126" t="str">
+      <c r="P126" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -5999,12 +6757,18 @@
         <v>ឪពុក ហុង ពិសី</v>
       </c>
       <c r="L127" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M127" t="str">
         <v>ម្តាយ ហុង ពិសី</v>
       </c>
-      <c r="M127" t="str">
+      <c r="N127" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O127" t="str">
         <v>012 090 030</v>
       </c>
-      <c r="N127" t="str">
+      <c r="P127" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6043,12 +6807,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L128" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M128" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O128" t="str">
         <v>012 090 031</v>
       </c>
-      <c r="N128" t="str">
+      <c r="P128" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6087,12 +6857,18 @@
         <v>ឪពុក សោម ចរិយា</v>
       </c>
       <c r="L129" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M129" t="str">
         <v>ម្តាយ សោម ចរិយា</v>
       </c>
-      <c r="M129" t="str">
+      <c r="N129" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O129" t="str">
         <v>012 090 032</v>
       </c>
-      <c r="N129" t="str">
+      <c r="P129" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6131,12 +6907,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L130" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M130" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M130" t="str">
+      <c r="N130" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O130" t="str">
         <v>012 090 033</v>
       </c>
-      <c r="N130" t="str">
+      <c r="P130" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6175,12 +6957,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L131" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M131" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M131" t="str">
+      <c r="N131" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O131" t="str">
         <v>012 090 034</v>
       </c>
-      <c r="N131" t="str">
+      <c r="P131" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6219,12 +7007,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L132" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M132" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M132" t="str">
+      <c r="N132" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O132" t="str">
         <v>012 090 035</v>
       </c>
-      <c r="N132" t="str">
+      <c r="P132" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6263,12 +7057,18 @@
         <v>ឪពុក ហុង សម្បត្តិ</v>
       </c>
       <c r="L133" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M133" t="str">
         <v>ម្តាយ ហុង សម្បត្តិ</v>
       </c>
-      <c r="M133" t="str">
+      <c r="N133" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O133" t="str">
         <v>012 060 001</v>
       </c>
-      <c r="N133" t="str">
+      <c r="P133" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6307,12 +7107,18 @@
         <v>ឪពុក ទេព ធីតា</v>
       </c>
       <c r="L134" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M134" t="str">
         <v>ម្តាយ ទេព ធីតា</v>
       </c>
-      <c r="M134" t="str">
+      <c r="N134" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O134" t="str">
         <v>012 060 002</v>
       </c>
-      <c r="N134" t="str">
+      <c r="P134" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6351,12 +7157,18 @@
         <v>ឪពុក កែវ សុខា</v>
       </c>
       <c r="L135" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M135" t="str">
         <v>ម្តាយ កែវ សុខា</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O135" t="str">
         <v>012 060 003</v>
       </c>
-      <c r="N135" t="str">
+      <c r="P135" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6395,12 +7207,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L136" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M136" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M136" t="str">
+      <c r="N136" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O136" t="str">
         <v>012 060 004</v>
       </c>
-      <c r="N136" t="str">
+      <c r="P136" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6439,12 +7257,18 @@
         <v>ឪពុក លី សុខុម</v>
       </c>
       <c r="L137" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M137" t="str">
         <v>ម្តាយ លី សុខុម</v>
       </c>
-      <c r="M137" t="str">
+      <c r="N137" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O137" t="str">
         <v>012 060 005</v>
       </c>
-      <c r="N137" t="str">
+      <c r="P137" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6483,12 +7307,18 @@
         <v>ឪពុក ហេង សុជាតា</v>
       </c>
       <c r="L138" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M138" t="str">
         <v>ម្តាយ ហេង សុជាតា</v>
       </c>
-      <c r="M138" t="str">
+      <c r="N138" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O138" t="str">
         <v>012 060 006</v>
       </c>
-      <c r="N138" t="str">
+      <c r="P138" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6527,12 +7357,18 @@
         <v>ឪពុក ម៉ៅ ចិន្តា</v>
       </c>
       <c r="L139" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M139" t="str">
         <v>ម្តាយ ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M139" t="str">
+      <c r="N139" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O139" t="str">
         <v>012 060 007</v>
       </c>
-      <c r="N139" t="str">
+      <c r="P139" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6571,12 +7407,18 @@
         <v>ឪពុក សេង មុនីកា</v>
       </c>
       <c r="L140" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M140" t="str">
         <v>ម្តាយ សេង មុនីកា</v>
       </c>
-      <c r="M140" t="str">
+      <c r="N140" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O140" t="str">
         <v>012 060 008</v>
       </c>
-      <c r="N140" t="str">
+      <c r="P140" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6615,12 +7457,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L141" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M141" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M141" t="str">
+      <c r="N141" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O141" t="str">
         <v>012 060 009</v>
       </c>
-      <c r="N141" t="str">
+      <c r="P141" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6659,12 +7507,18 @@
         <v>ឪពុក យឹម ស្រីនីត</v>
       </c>
       <c r="L142" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M142" t="str">
         <v>ម្តាយ យឹម ស្រីនីត</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O142" t="str">
         <v>012 060 010</v>
       </c>
-      <c r="N142" t="str">
+      <c r="P142" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6703,12 +7557,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L143" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M143" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M143" t="str">
+      <c r="N143" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O143" t="str">
         <v>012 060 011</v>
       </c>
-      <c r="N143" t="str">
+      <c r="P143" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6747,12 +7607,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L144" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M144" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M144" t="str">
+      <c r="N144" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O144" t="str">
         <v>012 060 012</v>
       </c>
-      <c r="N144" t="str">
+      <c r="P144" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6791,12 +7657,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L145" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M145" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M145" t="str">
+      <c r="N145" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O145" t="str">
         <v>012 060 013</v>
       </c>
-      <c r="N145" t="str">
+      <c r="P145" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6835,12 +7707,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L146" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M146" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M146" t="str">
+      <c r="N146" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O146" t="str">
         <v>012 060 014</v>
       </c>
-      <c r="N146" t="str">
+      <c r="P146" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6879,12 +7757,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L147" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M147" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M147" t="str">
+      <c r="N147" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O147" t="str">
         <v>012 060 015</v>
       </c>
-      <c r="N147" t="str">
+      <c r="P147" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6923,12 +7807,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L148" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M148" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M148" t="str">
+      <c r="N148" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O148" t="str">
         <v>012 060 016</v>
       </c>
-      <c r="N148" t="str">
+      <c r="P148" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -6967,12 +7857,18 @@
         <v>ឪពុក ហុង សម្បត្តិ</v>
       </c>
       <c r="L149" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M149" t="str">
         <v>ម្តាយ ហុង សម្បត្តិ</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O149" t="str">
         <v>012 060 017</v>
       </c>
-      <c r="N149" t="str">
+      <c r="P149" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7011,12 +7907,18 @@
         <v>ឪពុក ទេព ធីតា</v>
       </c>
       <c r="L150" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M150" t="str">
         <v>ម្តាយ ទេព ធីតា</v>
       </c>
-      <c r="M150" t="str">
+      <c r="N150" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O150" t="str">
         <v>012 060 018</v>
       </c>
-      <c r="N150" t="str">
+      <c r="P150" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7055,12 +7957,18 @@
         <v>ឪពុក កែវ សុខា</v>
       </c>
       <c r="L151" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M151" t="str">
         <v>ម្តាយ កែវ សុខា</v>
       </c>
-      <c r="M151" t="str">
+      <c r="N151" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O151" t="str">
         <v>012 060 019</v>
       </c>
-      <c r="N151" t="str">
+      <c r="P151" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7099,12 +8007,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L152" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M152" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M152" t="str">
+      <c r="N152" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O152" t="str">
         <v>012 060 020</v>
       </c>
-      <c r="N152" t="str">
+      <c r="P152" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7143,12 +8057,18 @@
         <v>ឪពុក លី សុខុម</v>
       </c>
       <c r="L153" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M153" t="str">
         <v>ម្តាយ លី សុខុម</v>
       </c>
-      <c r="M153" t="str">
+      <c r="N153" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O153" t="str">
         <v>012 060 021</v>
       </c>
-      <c r="N153" t="str">
+      <c r="P153" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7187,12 +8107,18 @@
         <v>ឪពុក ហេង សុជាតា</v>
       </c>
       <c r="L154" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M154" t="str">
         <v>ម្តាយ ហេង សុជាតា</v>
       </c>
-      <c r="M154" t="str">
+      <c r="N154" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O154" t="str">
         <v>012 060 022</v>
       </c>
-      <c r="N154" t="str">
+      <c r="P154" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7231,12 +8157,18 @@
         <v>ឪពុក ម៉ៅ ចិន្តា</v>
       </c>
       <c r="L155" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M155" t="str">
         <v>ម្តាយ ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M155" t="str">
+      <c r="N155" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O155" t="str">
         <v>012 060 023</v>
       </c>
-      <c r="N155" t="str">
+      <c r="P155" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7275,12 +8207,18 @@
         <v>ឪពុក សេង មុនីកា</v>
       </c>
       <c r="L156" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M156" t="str">
         <v>ម្តាយ សេង មុនីកា</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O156" t="str">
         <v>012 060 024</v>
       </c>
-      <c r="N156" t="str">
+      <c r="P156" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7319,12 +8257,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L157" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M157" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M157" t="str">
+      <c r="N157" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O157" t="str">
         <v>012 060 025</v>
       </c>
-      <c r="N157" t="str">
+      <c r="P157" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7363,12 +8307,18 @@
         <v>ឪពុក យឹម ស្រីនីត</v>
       </c>
       <c r="L158" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M158" t="str">
         <v>ម្តាយ យឹម ស្រីនីត</v>
       </c>
-      <c r="M158" t="str">
+      <c r="N158" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O158" t="str">
         <v>012 060 026</v>
       </c>
-      <c r="N158" t="str">
+      <c r="P158" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7407,12 +8357,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L159" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M159" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M159" t="str">
+      <c r="N159" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O159" t="str">
         <v>012 060 027</v>
       </c>
-      <c r="N159" t="str">
+      <c r="P159" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7451,12 +8407,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L160" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M160" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M160" t="str">
+      <c r="N160" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O160" t="str">
         <v>012 060 028</v>
       </c>
-      <c r="N160" t="str">
+      <c r="P160" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7495,12 +8457,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L161" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M161" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M161" t="str">
+      <c r="N161" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O161" t="str">
         <v>012 060 029</v>
       </c>
-      <c r="N161" t="str">
+      <c r="P161" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7539,12 +8507,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L162" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M162" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M162" t="str">
+      <c r="N162" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O162" t="str">
         <v>012 060 030</v>
       </c>
-      <c r="N162" t="str">
+      <c r="P162" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7583,12 +8557,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L163" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M163" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M163" t="str">
+      <c r="N163" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O163" t="str">
         <v>012 060 031</v>
       </c>
-      <c r="N163" t="str">
+      <c r="P163" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7627,25 +8607,31 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L164" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M164" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M164" t="str">
+      <c r="N164" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O164" t="str">
         <v>012 060 032</v>
       </c>
-      <c r="N164" t="str">
+      <c r="P164" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P164"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:P31"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -7658,9 +8644,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7698,12 +8686,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -7742,12 +8736,18 @@
         <v>ចាន់ សុខា</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>កែវ ស្រីពៅ</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 341 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7786,12 +8786,18 @@
         <v>សុខ ចាន់ថន</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>089 667 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7830,12 +8836,18 @@
         <v>ហេង សម្បត្តិ</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ឡុង ធីតា</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>017 889 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7874,12 +8886,18 @@
         <v>គង់ សុវណ្ណ</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>សេង មុនីកា</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>098 554 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7918,12 +8936,18 @@
         <v>ម៉ៅ វិចិត្រ</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ទាវ សុផល</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>070 223 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -7962,12 +8986,18 @@
         <v>ឈុន សំអាត</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ង៉ែត សុភ័ក្រ</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>011 445 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8006,12 +9036,18 @@
         <v>តាំង ហុកសេង</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>លឹម គឹមហួរ</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 998 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8050,12 +9086,18 @@
         <v>ស៊ុន វណ្ណារ៉ា</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>យឹម ស្រីនាង</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>097 334 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8094,12 +9136,18 @@
         <v>លាង សុវណ្ណ</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>សោម ចរិយា</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>015 776 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8138,12 +9186,18 @@
         <v>អ៊ុំ សារ៉េត</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ពៅ សុភី</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>085 221 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8182,12 +9236,18 @@
         <v>ឌួង រិទ្ធី</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>លាង សុខេង</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>077 889 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8226,12 +9286,18 @@
         <v>នូ សារុន</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ហុង ពិសី</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>096 443 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8270,12 +9336,18 @@
         <v>ឡាយ សុវណ្ណា</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ជុំ ចរិយា</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 667 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8314,12 +9386,18 @@
         <v>វ៉ាន់ គង់</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>សោម ធីតា</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>098 112 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8358,12 +9436,18 @@
         <v>ជា សុវណ្ណ</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម៉ៅ គឹមលាង</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>089 334 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8402,12 +9486,18 @@
         <v>កែវ សុជាតិ</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ស៊ុន ផល្លា</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>017 556 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8446,12 +9536,18 @@
         <v>រស់ គឹមស៊ន</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ខៀវ គឹមអាន</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>010 778 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8490,12 +9586,18 @@
         <v>សេង វណ្ណឌី</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 889 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8534,12 +9636,18 @@
         <v>ណុប ផល</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ចាន់ ស្រីអូន</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>077 990 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8578,12 +9686,18 @@
         <v>យឹម វិចិត្រ</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម៉ី សុខុម</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>061 223 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8622,12 +9736,18 @@
         <v>អ៊ុក គឹមហេង</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ចាន់ ស្រីមុំ</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 445 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8666,12 +9786,18 @@
         <v>ហុង សារ៉ុម</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>នូ សារុន</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>015 667 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8710,12 +9836,18 @@
         <v>លី សុខុម</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ទេព ធីតា</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>097 889 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8754,12 +9886,18 @@
         <v>ទេព សុវណ្ណ</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>070 112 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8798,12 +9936,18 @@
         <v>ពេជ្រ សារ៉េត</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>សេង ផល្លា</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>089 443 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8842,12 +9986,18 @@
         <v>សោម ប៊ុនធឿន</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម៉ៅ វណ្ណី</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>016 554 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8886,12 +10036,18 @@
         <v>ខៀវ គឹមអាន</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>រស់ សុភី</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 334 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8930,12 +10086,18 @@
         <v>ភួង សំអុល</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ចាន់ ស្រីមុំ</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>098 776 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -8974,12 +10136,18 @@
         <v>អៀង វណ្ណា</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ឡាយ ស្រីពៅ</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>085 990 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9018,25 +10186,31 @@
         <v>ឡុង វិចិត្រ</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ស៊ុន ធីតា</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>017 221 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:P33"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -9049,9 +10223,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9089,12 +10265,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -9133,12 +10315,18 @@
         <v>ឪពុក សុខ រិទ្ធី</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>ម្តាយ សុខ រិទ្ធី</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 150 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9177,12 +10365,18 @@
         <v>ឪពុក សុខ ស្រីពេជ្រ</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម្តាយ សុខ ស្រីពេជ្រ</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>012 150 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9221,12 +10415,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>012 150 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9265,12 +10465,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>012 150 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9309,12 +10515,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>012 150 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9353,12 +10565,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>012 150 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9397,12 +10615,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 150 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9441,12 +10665,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>012 150 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9485,12 +10715,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>012 150 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9529,12 +10765,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>012 150 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9573,12 +10815,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>012 150 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9617,12 +10865,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>012 150 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9661,12 +10915,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 150 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9705,12 +10965,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>012 150 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9749,12 +11015,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>012 150 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9793,12 +11065,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>012 150 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9837,12 +11115,18 @@
         <v>ឪពុក សុខ រិទ្ធី</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ម្តាយ សុខ រិទ្ធី</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>012 150 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9881,12 +11165,18 @@
         <v>ឪពុក សុខ ស្រីពេជ្រ</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ម្តាយ សុខ ស្រីពេជ្រ</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 150 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9925,12 +11215,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>012 150 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -9969,12 +11265,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>012 150 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10013,12 +11315,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 150 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10057,12 +11365,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>012 150 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10101,12 +11415,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>012 150 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10145,12 +11465,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>012 150 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10189,12 +11515,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>012 150 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10233,12 +11565,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>012 150 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10277,12 +11615,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 150 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10321,12 +11665,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>012 150 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10365,12 +11715,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>012 150 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10409,12 +11765,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>012 150 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10453,12 +11815,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L32" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M32" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O32" t="str">
         <v>012 150 031</v>
       </c>
-      <c r="N32" t="str">
+      <c r="P32" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10497,25 +11865,31 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L33" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M33" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O33" t="str">
         <v>012 150 032</v>
       </c>
-      <c r="N33" t="str">
+      <c r="P33" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:P35"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -10528,9 +11902,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10568,12 +11944,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -10612,12 +11994,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 130 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10656,12 +12044,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>012 130 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10700,12 +12094,18 @@
         <v>ឪពុក ចាន់ សុភ័ក្ត្រ</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ម្តាយ ចាន់ សុភ័ក្ត្រ</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>012 130 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10744,12 +12144,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>012 130 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10788,12 +12194,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>012 130 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10832,12 +12244,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>012 130 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10876,12 +12294,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 130 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10920,12 +12344,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>012 130 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -10964,12 +12394,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>012 130 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11008,12 +12444,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>012 130 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11052,12 +12494,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>012 130 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11096,12 +12544,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>012 130 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11140,12 +12594,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 130 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11184,12 +12644,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>012 130 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11228,12 +12694,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>012 130 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11272,12 +12744,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>012 130 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11316,12 +12794,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>012 130 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11360,12 +12844,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 130 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11404,12 +12894,18 @@
         <v>ឪពុក ចាន់ សុភ័ក្ត្រ</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ម្តាយ ចាន់ សុភ័ក្ត្រ</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>012 130 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11448,12 +12944,18 @@
         <v>ឪពុក គង់ ម៉ាលីកា</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម្តាយ គង់ ម៉ាលីកា</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>012 130 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11492,12 +12994,18 @@
         <v>ឪពុក ម៉ៅ ពិសិដ្ឋ</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ម្តាយ ម៉ៅ ពិសិដ្ឋ</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 130 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11536,12 +13044,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>012 130 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11580,12 +13094,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>012 130 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11624,12 +13144,18 @@
         <v>ឪពុក ស៊ុន ចរិយា</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>ម្តាយ ស៊ុន ចរិយា</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>012 130 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11668,12 +13194,18 @@
         <v>ឪពុក លាង រតនៈ</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>ម្តាយ លាង រតនៈ</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>012 130 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11712,12 +13244,18 @@
         <v>ឪពុក អ៊ុំ ពិសី</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម្តាយ អ៊ុំ ពិសី</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>012 130 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11756,12 +13294,18 @@
         <v>ឪពុក ឌួង ចាន់ដារ៉ា</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>ម្តាយ ឌួង ចាន់ដារ៉ា</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 130 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11800,12 +13344,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>012 130 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11844,12 +13394,18 @@
         <v>ឪពុក ឡាយ ឧត្តម</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ម្តាយ ឡាយ ឧត្តម</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>012 130 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11888,12 +13444,18 @@
         <v>ឪពុក វ៉ាន់ ស្រីអូន</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ម្តាយ វ៉ាន់ ស្រីអូន</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>012 130 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11932,12 +13494,18 @@
         <v>ឪពុក ជា សុវណ្ណារ៉ា</v>
       </c>
       <c r="L32" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M32" t="str">
         <v>ម្តាយ ជា សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O32" t="str">
         <v>012 130 031</v>
       </c>
-      <c r="N32" t="str">
+      <c r="P32" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -11976,12 +13544,18 @@
         <v>ឪពុក រស់ ស្រីលក្ខណ៍</v>
       </c>
       <c r="L33" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M33" t="str">
         <v>ម្តាយ រស់ ស្រីលក្ខណ៍</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O33" t="str">
         <v>012 130 032</v>
       </c>
-      <c r="N33" t="str">
+      <c r="P33" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12020,12 +13594,18 @@
         <v>ឪពុក ហេង វិបុល</v>
       </c>
       <c r="L34" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M34" t="str">
         <v>ម្តាយ ហេង វិបុល</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O34" t="str">
         <v>012 130 033</v>
       </c>
-      <c r="N34" t="str">
+      <c r="P34" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12064,25 +13644,31 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L35" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M35" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O35" t="str">
         <v>012 130 034</v>
       </c>
-      <c r="N35" t="str">
+      <c r="P35" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:P36"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -12095,9 +13681,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12135,12 +13723,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -12179,12 +13773,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 090 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12223,12 +13823,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>012 090 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12267,12 +13873,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>012 090 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12311,12 +13923,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>012 090 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12355,12 +13973,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>012 090 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12399,12 +14023,18 @@
         <v>ឪពុក លឹម គឹមហួរ</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ម្តាយ លឹម គឹមហួរ</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>012 090 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12443,12 +14073,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 090 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12487,12 +14123,18 @@
         <v>ឪពុក អ៊ុក ស្រីពេជ្រ</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>ម្តាយ អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>012 090 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12531,12 +14173,18 @@
         <v>ឪពុក សេង វណ្ណឌី</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>ម្តាយ សេង វណ្ណឌី</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>012 090 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12575,12 +14223,18 @@
         <v>ឪពុក ឈុន សុភ័ក្ត្រ</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ម្តាយ ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>012 090 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12619,12 +14273,18 @@
         <v>ឪពុក ឈុន ពិសិដ្ឋ</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>ម្តាយ ឈុន ពិសិដ្ឋ</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>012 090 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12663,12 +14323,18 @@
         <v>ឪពុក ស៊ុន ស្រីកែវ</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ម្តាយ ស៊ុន ស្រីកែវ</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>012 090 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12707,12 +14373,18 @@
         <v>ឪពុក ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ម្តាយ ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 090 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12751,12 +14423,18 @@
         <v>ឪពុក ហុង ពិសី</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>ម្តាយ ហុង ពិសី</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>012 090 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12795,12 +14473,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>012 090 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12839,12 +14523,18 @@
         <v>ឪពុក សោម ចរិយា</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ម្តាយ សោម ចរិយា</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>012 090 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12883,12 +14573,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>012 090 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12927,12 +14623,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 090 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -12971,12 +14673,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>012 090 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13015,12 +14723,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>012 090 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13059,12 +14773,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 090 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13103,12 +14823,18 @@
         <v>ឪពុក លឹម គឹមហួរ</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>ម្តាយ លឹម គឹមហួរ</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>012 090 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13147,12 +14873,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>012 090 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13191,12 +14923,18 @@
         <v>ឪពុក អ៊ុក ស្រីពេជ្រ</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>ម្តាយ អ៊ុក ស្រីពេជ្រ</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>012 090 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13235,12 +14973,18 @@
         <v>ឪពុក សេង វណ្ណឌី</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>ម្តាយ សេង វណ្ណឌី</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>012 090 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13279,12 +15023,18 @@
         <v>ឪពុក ឈុន សុភ័ក្ត្រ</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម្តាយ ឈុន សុភ័ក្ត្រ</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>012 090 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13323,12 +15073,18 @@
         <v>ឪពុក ឈុន ពិសិដ្ឋ</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>ម្តាយ ឈុន ពិសិដ្ឋ</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 090 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13367,12 +15123,18 @@
         <v>ឪពុក ស៊ុន ស្រីកែវ</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ម្តាយ ស៊ុន ស្រីកែវ</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>012 090 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13411,12 +15173,18 @@
         <v>ឪពុក ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ម្តាយ ស៊ុន សុវណ្ណារ៉ា</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>012 090 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13455,12 +15223,18 @@
         <v>ឪពុក ហុង ពិសី</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ម្តាយ ហុង ពិសី</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>012 090 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13499,12 +15273,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L32" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M32" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O32" t="str">
         <v>012 090 031</v>
       </c>
-      <c r="N32" t="str">
+      <c r="P32" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13543,12 +15323,18 @@
         <v>ឪពុក សោម ចរិយា</v>
       </c>
       <c r="L33" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M33" t="str">
         <v>ម្តាយ សោម ចរិយា</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O33" t="str">
         <v>012 090 032</v>
       </c>
-      <c r="N33" t="str">
+      <c r="P33" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13587,12 +15373,18 @@
         <v>ឪពុក អ៊ុក សុធារ៉ា</v>
       </c>
       <c r="L34" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M34" t="str">
         <v>ម្តាយ អ៊ុក សុធារ៉ា</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O34" t="str">
         <v>012 090 033</v>
       </c>
-      <c r="N34" t="str">
+      <c r="P34" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13631,12 +15423,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L35" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M35" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O35" t="str">
         <v>012 090 034</v>
       </c>
-      <c r="N35" t="str">
+      <c r="P35" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13675,25 +15473,31 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L36" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M36" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O36" t="str">
         <v>012 090 035</v>
       </c>
-      <c r="N36" t="str">
+      <c r="P36" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:P33"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -13706,9 +15510,11 @@
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13746,12 +15552,18 @@
         <v>ឈ្មោះឪពុក (Father Name)</v>
       </c>
       <c r="L1" t="str">
+        <v>មុខរបរឪពុក (Father Occupation)</v>
+      </c>
+      <c r="M1" t="str">
         <v>ឈ្មោះម្តាយ (Mother Name)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
+        <v>មុខរបរម្តាយ (Mother Occupation)</v>
+      </c>
+      <c r="O1" t="str">
         <v>លេខទូរស័ព្ទអាណាព្យាបាល (Guardian Phone)</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>ស្ថានភាព (Status)</v>
       </c>
     </row>
@@ -13790,12 +15602,18 @@
         <v>ឪពុក ហុង សម្បត្តិ</v>
       </c>
       <c r="L2" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M2" t="str">
         <v>ម្តាយ ហុង សម្បត្តិ</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O2" t="str">
         <v>012 060 001</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13834,12 +15652,18 @@
         <v>ឪពុក ទេព ធីតា</v>
       </c>
       <c r="L3" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M3" t="str">
         <v>ម្តាយ ទេព ធីតា</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O3" t="str">
         <v>012 060 002</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13878,12 +15702,18 @@
         <v>ឪពុក កែវ សុខា</v>
       </c>
       <c r="L4" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M4" t="str">
         <v>ម្តាយ កែវ សុខា</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O4" t="str">
         <v>012 060 003</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13922,12 +15752,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L5" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M5" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O5" t="str">
         <v>012 060 004</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -13966,12 +15802,18 @@
         <v>ឪពុក លី សុខុម</v>
       </c>
       <c r="L6" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M6" t="str">
         <v>ម្តាយ លី សុខុម</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O6" t="str">
         <v>012 060 005</v>
       </c>
-      <c r="N6" t="str">
+      <c r="P6" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14010,12 +15852,18 @@
         <v>ឪពុក ហេង សុជាតា</v>
       </c>
       <c r="L7" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M7" t="str">
         <v>ម្តាយ ហេង សុជាតា</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O7" t="str">
         <v>012 060 006</v>
       </c>
-      <c r="N7" t="str">
+      <c r="P7" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14054,12 +15902,18 @@
         <v>ឪពុក ម៉ៅ ចិន្តា</v>
       </c>
       <c r="L8" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M8" t="str">
         <v>ម្តាយ ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O8" t="str">
         <v>012 060 007</v>
       </c>
-      <c r="N8" t="str">
+      <c r="P8" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14098,12 +15952,18 @@
         <v>ឪពុក សេង មុនីកា</v>
       </c>
       <c r="L9" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M9" t="str">
         <v>ម្តាយ សេង មុនីកា</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O9" t="str">
         <v>012 060 008</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14142,12 +16002,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L10" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M10" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O10" t="str">
         <v>012 060 009</v>
       </c>
-      <c r="N10" t="str">
+      <c r="P10" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14186,12 +16052,18 @@
         <v>ឪពុក យឹម ស្រីនីត</v>
       </c>
       <c r="L11" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M11" t="str">
         <v>ម្តាយ យឹម ស្រីនីត</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O11" t="str">
         <v>012 060 010</v>
       </c>
-      <c r="N11" t="str">
+      <c r="P11" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14230,12 +16102,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L12" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M12" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O12" t="str">
         <v>012 060 011</v>
       </c>
-      <c r="N12" t="str">
+      <c r="P12" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14274,12 +16152,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L13" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M13" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O13" t="str">
         <v>012 060 012</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14318,12 +16202,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L14" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M14" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O14" t="str">
         <v>012 060 013</v>
       </c>
-      <c r="N14" t="str">
+      <c r="P14" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14362,12 +16252,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L15" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M15" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O15" t="str">
         <v>012 060 014</v>
       </c>
-      <c r="N15" t="str">
+      <c r="P15" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14406,12 +16302,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L16" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M16" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O16" t="str">
         <v>012 060 015</v>
       </c>
-      <c r="N16" t="str">
+      <c r="P16" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14450,12 +16352,18 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L17" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M17" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O17" t="str">
         <v>012 060 016</v>
       </c>
-      <c r="N17" t="str">
+      <c r="P17" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14494,12 +16402,18 @@
         <v>ឪពុក ហុង សម្បត្តិ</v>
       </c>
       <c r="L18" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M18" t="str">
         <v>ម្តាយ ហុង សម្បត្តិ</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O18" t="str">
         <v>012 060 017</v>
       </c>
-      <c r="N18" t="str">
+      <c r="P18" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14538,12 +16452,18 @@
         <v>ឪពុក ទេព ធីតា</v>
       </c>
       <c r="L19" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M19" t="str">
         <v>ម្តាយ ទេព ធីតា</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O19" t="str">
         <v>012 060 018</v>
       </c>
-      <c r="N19" t="str">
+      <c r="P19" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14582,12 +16502,18 @@
         <v>ឪពុក កែវ សុខា</v>
       </c>
       <c r="L20" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M20" t="str">
         <v>ម្តាយ កែវ សុខា</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O20" t="str">
         <v>012 060 019</v>
       </c>
-      <c r="N20" t="str">
+      <c r="P20" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14626,12 +16552,18 @@
         <v>ឪពុក កែវ ធីតា</v>
       </c>
       <c r="L21" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M21" t="str">
         <v>ម្តាយ កែវ ធីតា</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O21" t="str">
         <v>012 060 020</v>
       </c>
-      <c r="N21" t="str">
+      <c r="P21" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14670,12 +16602,18 @@
         <v>ឪពុក លី សុខុម</v>
       </c>
       <c r="L22" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M22" t="str">
         <v>ម្តាយ លី សុខុម</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O22" t="str">
         <v>012 060 021</v>
       </c>
-      <c r="N22" t="str">
+      <c r="P22" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14714,12 +16652,18 @@
         <v>ឪពុក ហេង សុជាតា</v>
       </c>
       <c r="L23" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M23" t="str">
         <v>ម្តាយ ហេង សុជាតា</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O23" t="str">
         <v>012 060 022</v>
       </c>
-      <c r="N23" t="str">
+      <c r="P23" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14758,12 +16702,18 @@
         <v>ឪពុក ម៉ៅ ចិន្តា</v>
       </c>
       <c r="L24" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="M24" t="str">
         <v>ម្តាយ ម៉ៅ ចិន្តា</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="O24" t="str">
         <v>012 060 023</v>
       </c>
-      <c r="N24" t="str">
+      <c r="P24" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14802,12 +16752,18 @@
         <v>ឪពុក សេង មុនីកា</v>
       </c>
       <c r="L25" t="str">
+        <v>គ្រូបង្រៀន</v>
+      </c>
+      <c r="M25" t="str">
         <v>ម្តាយ សេង មុនីកា</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="O25" t="str">
         <v>012 060 024</v>
       </c>
-      <c r="N25" t="str">
+      <c r="P25" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14846,12 +16802,18 @@
         <v>ឪពុក ឡាយ ប៊ុនរ៉ុង</v>
       </c>
       <c r="L26" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="M26" t="str">
         <v>ម្តាយ ឡាយ ប៊ុនរ៉ុង</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
+        <v>បុគ្គលិកធនាគារ</v>
+      </c>
+      <c r="O26" t="str">
         <v>012 060 025</v>
       </c>
-      <c r="N26" t="str">
+      <c r="P26" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14890,12 +16852,18 @@
         <v>ឪពុក យឹម ស្រីនីត</v>
       </c>
       <c r="L27" t="str">
+        <v>វិស្វករ</v>
+      </c>
+      <c r="M27" t="str">
         <v>ម្តាយ យឹម ស្រីនីត</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
+        <v>កសិករ</v>
+      </c>
+      <c r="O27" t="str">
         <v>012 060 026</v>
       </c>
-      <c r="N27" t="str">
+      <c r="P27" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14934,12 +16902,18 @@
         <v>ឪពុក តាំង គីមឡុង</v>
       </c>
       <c r="L28" t="str">
+        <v>ពាណិជ្ជករ</v>
+      </c>
+      <c r="M28" t="str">
         <v>ម្តាយ តាំង គីមឡុង</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
+        <v>គិលានុបដ្ឋាយិកា</v>
+      </c>
+      <c r="O28" t="str">
         <v>012 060 027</v>
       </c>
-      <c r="N28" t="str">
+      <c r="P28" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -14978,12 +16952,18 @@
         <v>ឪពុក ឈុន ស្រីមុំ</v>
       </c>
       <c r="L29" t="str">
+        <v>វេជ្ជបណ្ឌិត</v>
+      </c>
+      <c r="M29" t="str">
         <v>ម្តាយ ឈុន ស្រីមុំ</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
+        <v>សហគ្រិន</v>
+      </c>
+      <c r="O29" t="str">
         <v>012 060 028</v>
       </c>
-      <c r="N29" t="str">
+      <c r="P29" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -15022,12 +17002,18 @@
         <v>ឪពុក គង់ វណ្ណៈ</v>
       </c>
       <c r="L30" t="str">
+        <v>អ្នកបើកបរ</v>
+      </c>
+      <c r="M30" t="str">
         <v>ម្តាយ គង់ វណ្ណៈ</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
+        <v>បុគ្គលិកក្រុមហ៊ុន</v>
+      </c>
+      <c r="O30" t="str">
         <v>012 060 029</v>
       </c>
-      <c r="N30" t="str">
+      <c r="P30" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -15066,12 +17052,18 @@
         <v>ឪពុក នូ សុជាតា</v>
       </c>
       <c r="L31" t="str">
+        <v>មេការសំណង់</v>
+      </c>
+      <c r="M31" t="str">
         <v>ម្តាយ នូ សុជាតា</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
+        <v>អ្នកកាត់ដេរ</v>
+      </c>
+      <c r="O31" t="str">
         <v>012 060 030</v>
       </c>
-      <c r="N31" t="str">
+      <c r="P31" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -15110,12 +17102,18 @@
         <v>ឪពុក អ៊ុំ វិបុល</v>
       </c>
       <c r="L32" t="str">
+        <v>មន្ត្រីរាជការ</v>
+      </c>
+      <c r="M32" t="str">
         <v>ម្តាយ អ៊ុំ វិបុល</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="O32" t="str">
         <v>012 060 031</v>
       </c>
-      <c r="N32" t="str">
+      <c r="P32" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
@@ -15154,18 +17152,24 @@
         <v>ឪពុក ពៅ សុភី</v>
       </c>
       <c r="L33" t="str">
+        <v>អាជីវករ</v>
+      </c>
+      <c r="M33" t="str">
         <v>ម្តាយ ពៅ សុភី</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
+        <v>មេផ្ទះ</v>
+      </c>
+      <c r="O33" t="str">
         <v>012 060 032</v>
       </c>
-      <c r="N33" t="str">
+      <c r="P33" t="str">
         <v>កំពុងសិក្សា (Active)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P33"/>
   </ignoredErrors>
 </worksheet>
 </file>